--- a/daily_matches/job_matches_2026-06-16.xlsx
+++ b/daily_matches/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IKS Health</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>34.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Data Lake, Kinesis, Docker, Kubernetes, Apache Airflow, CI/CD</t>
+          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, NLTK, S3, Athena</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a12a261b9e6a632</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c843452e183915</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893d5e6eb990356d</t>
+          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407650b6fa832e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfa1270384948c8d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, PySpark, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ad316f0925858</t>
+          <t>https://www.indeed.com/viewjob?jk=327c3cad559a4b06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, CI/CD, PySpark, Kafka, MySQL, MongoDB, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc40f95617fae929</t>
+          <t>https://www.indeed.com/viewjob?jk=3c896322c2ead6db</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Quality Assurance Engineer - Cloud Services</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>BMG360</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, MySQL, MongoDB, Python</t>
+          <t>LangChain, S3, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b12bb149e3204420</t>
+          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
+          <t>AI Engineer, RAG, S3, Redshift, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1575e4dc7d31dc</t>
+          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Dev Engineer III</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, Kafka, NoSQL, Python, SQL</t>
+          <t>Copilot, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b39868d0c95a10</t>
+          <t>https://www.indeed.com/viewjob?jk=2821e316b5dc735e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Goal Family of Companies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL</t>
+          <t>Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d518da25369f319</t>
+          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineering Specialist</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243cab21a88de574</t>
+          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/ML Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Orbion Space Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houghton, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Kubernetes, PostgreSQL, Python</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf38b28c38090e5</t>
+          <t>https://www.indeed.com/viewjob?jk=11b29de58f725b70</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Science</t>
+          <t>Data Management Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Redshift, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=195fc60b7623d5b0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II Platform, AI Enablement</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd6bdba5413ba36</t>
+          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II Platform, Core Services</t>
+          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65723be5a35b13a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d71b9467031bd4b</t>
+          <t>https://www.indeed.com/viewjob?jk=4840cb3f1db3e27d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b417a9576d886823</t>
+          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>Data Scientist, RAG, CI/CD, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8235ea8b5474bc2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Full Stack Java Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971675e4d1607d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a34f8fb76f51825</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Aritzia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b47d8e4416d6909</t>
+          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Software Engineer - Agentic Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nCino</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>RAG, Docker, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bca14a08eaac583</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eaa8c67652862b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Research Scientist – Foundation Models &amp; Agentic AI</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Traversal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch, Git, R</t>
+          <t>AI Engineer, RAG, Pinecone, S3, FastAPI, Kubernetes, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c842ab65828f7bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc477a37c4cf841</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure, Databricks</t>
+          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Synapse, CI/CD, Git, Databricks, PySpark, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb5a8c81763658a8</t>
+          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Solutions</t>
+          <t>Data Scientist, Senior Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, BigQuery, Dataflow, CI/CD, BigQuery, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0aa2e523d258e41</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd762e2ad40da6f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, AI Driven Survey &amp; CSAT Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48640e1283f6197d</t>
+          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Price Optimization &amp; Bidding</t>
+          <t>Senior Full Stack Engineer - Contingent</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae014acf922aaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f76dc87b0998d19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Price Optimization &amp; Bidding</t>
+          <t>Senior Full Stack Engineer - Contingent</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Index Analytics LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Windsor Mill, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6706cecbaa1b0e65</t>
+          <t>https://www.indeed.com/viewjob?jk=9beb537749027352</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Extra Help - Institutional Research Data Coordinator - College of Medicine</t>
+          <t>Sr Software Engineer, AI Tools – On-Device Generative AI Model Optimization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>University of Illinois</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PyTorch, Databricks, PySpark, MySQL, Dask, Tableau, Matplotlib, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, LLaMA, Copilot, PyTorch, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ea796f4df21a1f</t>
+          <t>https://www.indeed.com/viewjob?jk=2714256eb3c47ac7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist, Revenue Cycle</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>City of Hope</t>
+          <t>Coloplast</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, Snowflake, Tableau, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Synapse, CI/CD, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564b426c666d85aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Services</t>
+          <t>Senior Front End Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e90cc663ef28ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=a761a82db21db9a9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Palantir Full Stack Engineer (React + Foundry)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Nova Web Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Git, Python, R, Scala</t>
+          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed927e60ed2b636b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b97af0270cc0c8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Forward Deployed AI Engineer, West</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Arize AI</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec6411fb70c7757</t>
+          <t>https://www.indeed.com/viewjob?jk=d3905f9ae184c480</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Python Unix machine learning Support Engineer</t>
+          <t>Senior Engineer, Backend</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>hatch IT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Matplotlib, Python, R, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, Kafka, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e9b34193625ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=e5c4c995337f4db1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Financial Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>United States Steel</t>
+          <t>PeopleConnect</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Hadoop, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84565e70a42ec3ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe14fbc3631ccd7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist Supervisor</t>
+          <t>Senior Business &amp; Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Heluna Health</t>
+          <t>Upgrade</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alhambra, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, SQL, R, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8820c698d507f</t>
+          <t>https://www.indeed.com/viewjob?jk=e250e0046419cb17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend/Java/Cloud</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Southern Glazer’s Wine &amp; Spirits</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Git, Kafka, Cassandra, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,77 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19320dd56902efd6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f059c9a011374c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Southern Glazer’s Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd78668066b9200b</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Southern Glazer’s Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dec170f6ffc23c52</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-16.xlsx
+++ b/daily_matches/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Ideas2IT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.4</v>
+        <v>28.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras, NLTK, S3, Athena</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c843452e183915</t>
+          <t>https://www.indeed.com/viewjob?jk=58202b65be5a1bb5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Palantir Foundry + TypeScript)</t>
+          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nova Web Technologies</t>
+          <t>LG Ad Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>28.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, S3, Glue, Athena, Redshift, Docker</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36ee9522c44ebe65</t>
+          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RVO Health</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa1270384948c8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RVO Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>Prompt Engineering, TensorFlow, PyTorch, Keras, S3, EC2, FastAPI, Docker, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327c3cad559a4b06</t>
+          <t>https://www.indeed.com/viewjob?jk=7bb23274bf8a259f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RVO Health</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c896322c2ead6db</t>
+          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BMG360</t>
+          <t>Dynatrace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, S3, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Python</t>
+          <t>Cortex, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5585f87e4193e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Digital Site Reliability Sr Engg.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Redshift, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af21378ee051eb56</t>
+          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>Data Scientist, RAG, CI/CD, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2821e316b5dc735e</t>
+          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular (Hybrid)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486cc12b5b77f742</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular(Hybrid)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Systems Planning and Analysis, Inc. (SPA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,207 +811,207 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c86f48f87c65a4</t>
+          <t>https://www.indeed.com/viewjob?jk=21b4f01facb33c82</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer in Consulting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Orbion Space Technology</t>
+          <t>Campana &amp; Schott Business Services GmbH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houghton, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, SQL</t>
+          <t>RAG, Data Lake, Docker, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11b29de58f725b70</t>
+          <t>https://www.indeed.com/viewjob?jk=34330ebc6f57ee63</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Management Specialist</t>
+          <t>Senior Software Engineer, Infrastructure Development</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb73c05264420df</t>
+          <t>https://www.indeed.com/viewjob?jk=3067f53491a2138d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Analytics Engineer, Music Creator Growth</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f21cc269f972fa3</t>
+          <t>https://www.indeed.com/viewjob?jk=e253aac59f209194</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer (Microservices &amp; Kafka)</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Sarepta Therapeutics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a03b545f1650339</t>
+          <t>https://www.indeed.com/viewjob?jk=afa2620282c4120e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer, Senior</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>ChowNow</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, Glue, AKS, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4840cb3f1db3e27d</t>
+          <t>https://www.indeed.com/viewjob?jk=6efb0adb320dd10a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer ( SQL , Python , ETL, Cloud )</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Hadoop, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04316e8a847eb128</t>
+          <t>https://www.indeed.com/viewjob?jk=b22fc4ba899c50ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c9f0a5349817ae</t>
+          <t>https://www.indeed.com/viewjob?jk=24d22b9e830921f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Java Development Engineer</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a34f8fb76f51825</t>
+          <t>https://www.indeed.com/viewjob?jk=648c09a1af4c1da7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Digital - Senior Data Engineer / Data Engineer, Digital Technology</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4183e5f7054ce4c5</t>
+          <t>https://www.indeed.com/viewjob?jk=daebb234970a494c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Agentic Platform</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nCino</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eaa8c67652862b</t>
+          <t>https://www.indeed.com/viewjob?jk=70e12748bbca3839</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Traversal</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, S3, FastAPI, Kubernetes, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc477a37c4cf841</t>
+          <t>https://www.indeed.com/viewjob?jk=190d0d1148301a38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Infrastructure/ DevOps Engineer, Fintech</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lazer</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1782bdcb28d52c8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff93e05503781548</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior Associate</t>
+          <t>Senior Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd762e2ad40da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=06210eed25c95bca</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Data Scientist - Corporate &amp; Institutional Banking</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d360efd4d04f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=aedf3a9b6d150ddd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Contingent</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>CliftonLarsonAllen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f76dc87b0998d19</t>
+          <t>https://www.indeed.com/viewjob?jk=b493af62ab0e210a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - Contingent</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Index Analytics LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Windsor Mill, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,402 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Copilot, Mistral, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9beb537749027352</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer, AI Tools – On-Device Generative AI Model Optimization</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, LLaMA, Copilot, PyTorch, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2714256eb3c47ac7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Coloplast</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6916823099c42d89</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Front End Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fidelity TalentSource</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a761a82db21db9a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Palantir Full Stack Engineer (React + Foundry)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Nova Web Technologies</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b97af0270cc0c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yarmouth, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3905f9ae184c480</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hatch IT</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kafka, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5c4c995337f4db1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Financial Data Analyst</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PeopleConnect</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe14fbc3631ccd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior Business &amp; Data Analyst</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Upgrade</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e250e0046419cb17</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Southern Glazer’s Wine &amp; Spirits</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Kirkland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f059c9a011374c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Southern Glazer’s Wine &amp; Spirits</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd78668066b9200b</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Southern Glazer’s Wine &amp; Spirits</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Kirkland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dec170f6ffc23c52</t>
+          <t>https://www.indeed.com/viewjob?jk=1d674db5503c5ec8</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-16.xlsx
+++ b/daily_matches/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ideas2IT</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Redshift, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58202b65be5a1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Reporting</t>
+          <t>Senior Software Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LG Ad Solutions</t>
+          <t>Signifyd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Redshift, BigQuery, Data Lake, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43e6726a3896fe03</t>
+          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Synapse, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6748d22408c01a3</t>
+          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Platform Engineer</t>
+          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Prompt Engineering, TensorFlow, PyTorch, Keras, S3, EC2, FastAPI, Docker, Kubernetes, Terraform</t>
+          <t>RAG, BigQuery, Docker, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb23274bf8a259f</t>
+          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, MLflow, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2337ec4ff54764f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dynatrace</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cortex, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e40e1e6f5dca3a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Digital Site Reliability Sr Engg.</t>
+          <t>Senior Software Engineer I or II- Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43a12edd3543ad18</t>
+          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Hadoop, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d04a3373d05f9f44</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Farmers Branch, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f1fbccd2f80abc</t>
+          <t>https://www.indeed.com/viewjob?jk=b6c450ef17454be8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Systems Planning and Analysis, Inc. (SPA)</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b4f01facb33c82</t>
+          <t>https://www.indeed.com/viewjob?jk=d438ffdb5156bae5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Developer in Consulting</t>
+          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Campana &amp; Schott Business Services GmbH</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Git, Snowflake, Databricks, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34330ebc6f57ee63</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure Development</t>
+          <t>AI and ML Platforms QA Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3067f53491a2138d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa078928c1c47a75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Music Creator Growth</t>
+          <t>Senior Software Engineer I &amp; II Platform, Core Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e253aac59f209194</t>
+          <t>https://www.indeed.com/viewjob?jk=fa9f2a2c2978c5b1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Engineer I &amp; II Platform, AI Enablement</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sarepta Therapeutics</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa2620282c4120e</t>
+          <t>https://www.indeed.com/viewjob?jk=12dd0aa275184bd2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Backend Engineer, Senior</t>
+          <t>Agentic AI Engineer - USC/GC/GC-EAD || W2 Role</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ChowNow</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Glue, AKS, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,199 +986,199 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efb0adb320dd10a</t>
+          <t>https://www.indeed.com/viewjob?jk=6582d65201534b1d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Infrastructure Support Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b22fc4ba899c50ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4426224b58c32b6a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Infrastructure Support Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>nSCALE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d22b9e830921f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7482d3d089b375a8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Engineer II, Software</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648c09a1af4c1da7</t>
+          <t>https://www.indeed.com/viewjob?jk=fc083035a1e84a16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Senior Software Engineer - Payments</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FastSpring</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daebb234970a494c</t>
+          <t>https://www.indeed.com/viewjob?jk=3095f789bd76d134</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Senior Data Scientist, Inventory 360 (Operations Research)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70e12748bbca3839</t>
+          <t>https://www.indeed.com/viewjob?jk=03eaf6d0909b62b6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=190d0d1148301a38</t>
+          <t>https://www.indeed.com/viewjob?jk=6173d6b7ca60683d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff93e05503781548</t>
+          <t>https://www.indeed.com/viewjob?jk=050b127fbd5b6847</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, SQL, R, Scala, Optimization</t>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06210eed25c95bca</t>
+          <t>https://www.indeed.com/viewjob?jk=884098cbfc5331d5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Scientist - Corporate &amp; Institutional Banking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedf3a9b6d150ddd</t>
+          <t>https://www.indeed.com/viewjob?jk=005bc717e1e9b14f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CliftonLarsonAllen</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b493af62ab0e210a</t>
+          <t>https://www.indeed.com/viewjob?jk=a93d3a23f194e7b2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Development Engineer I-1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Mistral, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,252 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d674db5503c5ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=50cb50da8c60ed84</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88a351beb562587f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TECHNICAL ENGINEER</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Atos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Aurora, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74e71df027563d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d567b0941743cab</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08a281f24bf37908</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Zvolvant</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cfe7ef7a354ce17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dimensional Fund Advisors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Kafka, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c747954af3731254</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>WeWork</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb8c5e992de9919</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-16.xlsx
+++ b/daily_matches/job_matches_2026-06-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, MLflow, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791f6ef1e634abe3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d3a6f7a359f862</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Platform</t>
+          <t>Data Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Signifyd</t>
+          <t>Blue Cross Blue Shield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Glue, Kubernetes, Snowflake, Databricks, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf19cbf47cdf97d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c16f06452db6a0f0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806890b9c74306d9</t>
+          <t>https://www.indeed.com/viewjob?jk=04544f5c224d0e1b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IT Data Engineer - Python/SQL (Onsite)</t>
+          <t>Sr Machine Learning Engineer( Austin only)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Autonomize AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Copilot, TensorFlow, PyTorch, OpenCV, Azure ML, MLflow, Snowflake, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=350b75002f62845f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bab7746885f266</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Optimus Health Analytics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bronx, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>S3, Glue, Athena, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3db9298181de6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9c73bd92ec32bb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer I - QuantumBlack, AI by McKinsey (Critical Industries)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, CI/CD, Terraform, Databricks, Dask, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e5216b64d140d5e</t>
+          <t>https://www.indeed.com/viewjob?jk=09d61f4f25722f32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I or II- Data Platform</t>
+          <t>Specialist, Yield Management - GTM AA Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Redshift, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, BigQuery, BigQuery, PySpark, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00fbc81ded39bdf</t>
+          <t>https://www.indeed.com/viewjob?jk=f3afc7189fd75646</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cassandra Database Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Cassandra, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe1b53272b4fe0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c8c2058057ef3c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI &amp; ML</t>
+          <t>Sr. Data Governance Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>ASSA ABLOY Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6c450ef17454be8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f812d27f7580652</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI &amp; ML</t>
+          <t>ML Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Data Lake, CI/CD, Terraform, Git, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d438ffdb5156bae5</t>
+          <t>https://www.indeed.com/viewjob?jk=60de930626b03451</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II - Platform, Identity</t>
+          <t>SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Atos</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a94bccdecb17d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d63d22402411d66</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI and ML Platforms QA Engineer III</t>
+          <t>Senior AI Engineer, Enterprise Agentic Solutions</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Terraform, Snowflake, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa078928c1c47a75</t>
+          <t>https://www.indeed.com/viewjob?jk=013a29a4eaecd85d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II Platform, Core Services</t>
+          <t>Sr Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Renaissance Learning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>RAG, Redshift, Docker, Kubernetes, CI/CD, Terraform, Git, Redshift, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa9f2a2c2978c5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b1e92ffe7b3df10a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I &amp; II Platform, AI Enablement</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dd0aa275184bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=489f25c5230f04c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer - USC/GC/GC-EAD || W2 Role</t>
+          <t>Software Engineer II - Supply Chain (REMOTE)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, Hugging Face, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6582d65201534b1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d09eae0579d4b37d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Infrastructure Support Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>OxeFit, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, Gemini, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4426224b58c32b6a</t>
+          <t>https://www.indeed.com/viewjob?jk=78edf9f6414d8ad1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Infrastructure Support Engineer</t>
+          <t>Machine Learning Engineer - Data Pipeline</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nSCALE</t>
+          <t>Articul8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7482d3d089b375a8</t>
+          <t>https://www.indeed.com/viewjob?jk=53ecaba2e1c87173</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Cons - Tech Cons-AI and Quantitative Modelling-AI Data Scientist-Senior-Multiple Positions-1717770</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, AKS, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc083035a1e84a16</t>
+          <t>https://www.indeed.com/viewjob?jk=d48cb703913ea89c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Payments</t>
+          <t>Infrastructure Software Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FastSpring</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Monett, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Git, PostgreSQL, NoSQL, SQL, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3095f789bd76d134</t>
+          <t>https://www.indeed.com/viewjob?jk=ee65a140c46c5d29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Inventory 360 (Operations Research)</t>
+          <t>Infrastructure Software Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eaf6d0909b62b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a146cfb932227c83</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>LangChain, Prompt Engineering, Kubernetes, Kafka, Hadoop, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6173d6b7ca60683d</t>
+          <t>https://www.indeed.com/viewjob?jk=4365a1b3f66a24d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>RAG, BigQuery, Dataflow, Apache Airflow, BigQuery, Kafka, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=050b127fbd5b6847</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1368e557d8b7ea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>LMTS AI Software Engineer - Agentforce Reasoning Engine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884098cbfc5331d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a41995f42e9d2c82</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=005bc717e1e9b14f</t>
+          <t>https://www.indeed.com/viewjob?jk=791267ed9d9650a3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wexford, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Synapse, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a93d3a23f194e7b2</t>
+          <t>https://www.indeed.com/viewjob?jk=bec0e3cae26d6c7f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer I-1</t>
+          <t>Data Scientist / AI Engineer (Agentic Systems &amp; Analytics)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>OxeFit, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Git, PostgreSQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50cb50da8c60ed84</t>
+          <t>https://www.indeed.com/viewjob?jk=f45c1bc71e433b4e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lean Solutions Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>Prompt Engineering, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88a351beb562587f</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd5afd9467221bf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TECHNICAL ENGINEER</t>
+          <t>Software Engineer 2, Full-stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Docker, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74e71df027563d27</t>
+          <t>https://www.indeed.com/viewjob?jk=58f214ed96d47bcb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data AI Engineer - Rates, Cost of Service, Load Forecasting Systems</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Juno Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Databricks, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d567b0941743cab</t>
+          <t>https://www.indeed.com/viewjob?jk=900b491af1585ba7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer II- Athlete Order (REMOTE)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a281f24bf37908</t>
+          <t>https://www.indeed.com/viewjob?jk=30ed9168436d79dd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zvolvant</t>
+          <t>SWBC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, Hadoop, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cfe7ef7a354ce17</t>
+          <t>https://www.indeed.com/viewjob?jk=fe8212d31e4446e1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Kafka, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c747954af3731254</t>
+          <t>https://www.indeed.com/viewjob?jk=f355fc6bd1303437</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WeWork</t>
+          <t>Neptune Flood</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Cortex, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,77 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbb8c5e992de9919</t>
+          <t>https://www.indeed.com/viewjob?jk=333c7eedb1144093</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Tableau, Power BI, Matplotlib, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b6d2f6637902b23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Richfield, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab534db9dc158d99</t>
         </is>
       </c>
     </row>
